--- a/宇川浚渫工事/着手前検討事項拾い出し資料.xlsx
+++ b/宇川浚渫工事/着手前検討事項拾い出し資料.xlsx
@@ -11,10 +11,11 @@
     <sheet name="進捗サマリ" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="工区別数量一覧（参考）" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="地元立会調整事項（工区別）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="想定降り口位置図" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'着手前検討事項チェックリスト'!$A$4:$I$20</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'着手前検討事項チェックリスト'!$A$4:$I$21</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'着手前検討事項チェックリスト'!$A$4:$I$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'地元立会調整事項（工区別）'!$A$4:$F$8</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'地元立会調整事項（工区別）'!$A$4:$F$9</definedName>
   </definedNames>
@@ -25,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="13">
     <font>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
@@ -98,6 +99,21 @@
       <family val="3"/>
       <sz val="6"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Yu Gothic"/>
+      <b val="1"/>
+      <color rgb="001F4E78"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Yu Gothic"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Yu Gothic"/>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="19">
@@ -264,7 +280,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -418,6 +434,9 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -515,6 +534,111 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5029200" cy="3228975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>29</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5029200" cy="3793331"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5029200" cy="3228975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>29</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5029200" cy="3793331"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1145,7 +1269,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="5" customWidth="1" style="47" min="1" max="1"/>
@@ -1939,7 +2063,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="84" customHeight="1" s="47">
+    <row r="21" ht="72" customHeight="1" s="47">
       <c r="A21" s="13" t="n">
         <v>17</v>
       </c>
@@ -1955,17 +2079,17 @@
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
-          <t>【調整漏れ】伊根町公共残土処分場における重機の降り口及び残土の搬出位置の確認</t>
+          <t>【調整漏れ】伊根町公共残土処分場の管理者との受入調整</t>
         </is>
       </c>
       <c r="E21" s="14" t="inlineStr">
         <is>
-          <t>伊根町本坂第2処分場について、重機の降り口（処分場内への重機の進入・降下位置）及び残土の搬出位置が未調整。ダンプの進入経路・転回場所、仮設（敷鉄板等）の要否とあわせて処分場管理者と現地確認し、施工計画に反映する。追加費用が生じる場合は監督職員と協議。</t>
+          <t>処分場（伊根町本坂第2処分場）側は管理者との調整のみ。搬入日時の予約、場内での荷下ろし位置・敷均しの取扱い等を処分場管理者と事前に調整する。重機の降り口は現場内で検討（No.18）。</t>
         </is>
       </c>
       <c r="F21" s="14" t="inlineStr">
         <is>
-          <t>伊根町（処分場管理者）／監督職員</t>
+          <t>伊根町（処分場管理者）</t>
         </is>
       </c>
       <c r="G21" s="13" t="inlineStr">
@@ -1981,6 +2105,54 @@
       <c r="I21" s="14" t="inlineStr">
         <is>
           <t>現場指摘による追加項目（No.8関連）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="110" customHeight="1" s="47">
+      <c r="A22" s="19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="19" t="inlineStr">
+        <is>
+          <t>工程・仮設計画</t>
+        </is>
+      </c>
+      <c r="C22" s="19" t="inlineStr">
+        <is>
+          <t>全工区</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>【調整漏れ】現場内の重機の降り口（河川内への進入位置）の選定</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>想定降り口は3～4箇所で可能（位置図：シート「想定降り口位置図」）。
+・本工事1：工区①・工区②の各1箇所（府道654号 井辺平線沿い）
+・本工事2：浚渫北側工区・浚渫南側工区の各1箇所
+地元立会時に位置を確認し、降り口の仮設（坂路・敷鉄板等）の要否、交通誘導、残土積込み位置とあわせて施工計画に反映する。</t>
+        </is>
+      </c>
+      <c r="F22" s="20" t="inlineStr">
+        <is>
+          <t>監督職員／地元関係者（地元立会）</t>
+        </is>
+      </c>
+      <c r="G22" s="19" t="inlineStr">
+        <is>
+          <t>地元立会時</t>
+        </is>
+      </c>
+      <c r="H22" s="19" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="I22" s="20" t="inlineStr">
+        <is>
+          <t>現場指摘による追加項目／想定降口位置図</t>
         </is>
       </c>
     </row>
@@ -1990,7 +2162,7 @@
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
   </mergeCells>
-  <conditionalFormatting sqref="H5:H21">
+  <conditionalFormatting sqref="H5:H22">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="2">
       <formula>"完了"</formula>
     </cfRule>
@@ -2002,7 +2174,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H5:H21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="H5:H22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"未着手,確認中,発注者協議中,完了"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2033,6 +2205,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="21.95" customHeight="1" s="47">
       <c r="A3" s="4" t="inlineStr">
         <is>
@@ -2072,23 +2245,23 @@
         </is>
       </c>
       <c r="B4" s="28">
-        <f>COUNTIF(着手前検討事項チェックリスト!$B$5:$B$21,A4)</f>
+        <f>COUNTIF(着手前検討事項チェックリスト!$B$5:$B$22,A4)</f>
         <v/>
       </c>
       <c r="C4" s="28">
-        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$21,A4,着手前検討事項チェックリスト!$H$5:$H$21,"未着手")</f>
+        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$22,A4,着手前検討事項チェックリスト!$H$5:$H$22,"未着手")</f>
         <v/>
       </c>
       <c r="D4" s="28">
-        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$21,A4,着手前検討事項チェックリスト!$H$5:$H$21,"確認中")</f>
+        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$22,A4,着手前検討事項チェックリスト!$H$5:$H$22,"確認中")</f>
         <v/>
       </c>
       <c r="E4" s="28">
-        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$21,A4,着手前検討事項チェックリスト!$H$5:$H$21,"発注者協議中")</f>
+        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$22,A4,着手前検討事項チェックリスト!$H$5:$H$22,"発注者協議中")</f>
         <v/>
       </c>
       <c r="F4" s="28">
-        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$21,A4,着手前検討事項チェックリスト!$H$5:$H$21,"完了")</f>
+        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$22,A4,着手前検討事項チェックリスト!$H$5:$H$22,"完了")</f>
         <v/>
       </c>
     </row>
@@ -2099,23 +2272,23 @@
         </is>
       </c>
       <c r="B5" s="28">
-        <f>COUNTIF(着手前検討事項チェックリスト!$B$5:$B$21,A5)</f>
+        <f>COUNTIF(着手前検討事項チェックリスト!$B$5:$B$22,A5)</f>
         <v/>
       </c>
       <c r="C5" s="28">
-        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$21,A5,着手前検討事項チェックリスト!$H$5:$H$21,"未着手")</f>
+        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$22,A5,着手前検討事項チェックリスト!$H$5:$H$22,"未着手")</f>
         <v/>
       </c>
       <c r="D5" s="28">
-        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$21,A5,着手前検討事項チェックリスト!$H$5:$H$21,"確認中")</f>
+        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$22,A5,着手前検討事項チェックリスト!$H$5:$H$22,"確認中")</f>
         <v/>
       </c>
       <c r="E5" s="28">
-        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$21,A5,着手前検討事項チェックリスト!$H$5:$H$21,"発注者協議中")</f>
+        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$22,A5,着手前検討事項チェックリスト!$H$5:$H$22,"発注者協議中")</f>
         <v/>
       </c>
       <c r="F5" s="28">
-        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$21,A5,着手前検討事項チェックリスト!$H$5:$H$21,"完了")</f>
+        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$22,A5,着手前検討事項チェックリスト!$H$5:$H$22,"完了")</f>
         <v/>
       </c>
     </row>
@@ -2126,23 +2299,23 @@
         </is>
       </c>
       <c r="B6" s="28">
-        <f>COUNTIF(着手前検討事項チェックリスト!$B$5:$B$21,A6)</f>
+        <f>COUNTIF(着手前検討事項チェックリスト!$B$5:$B$22,A6)</f>
         <v/>
       </c>
       <c r="C6" s="28">
-        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$21,A6,着手前検討事項チェックリスト!$H$5:$H$21,"未着手")</f>
+        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$22,A6,着手前検討事項チェックリスト!$H$5:$H$22,"未着手")</f>
         <v/>
       </c>
       <c r="D6" s="28">
-        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$21,A6,着手前検討事項チェックリスト!$H$5:$H$21,"確認中")</f>
+        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$22,A6,着手前検討事項チェックリスト!$H$5:$H$22,"確認中")</f>
         <v/>
       </c>
       <c r="E6" s="28">
-        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$21,A6,着手前検討事項チェックリスト!$H$5:$H$21,"発注者協議中")</f>
+        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$22,A6,着手前検討事項チェックリスト!$H$5:$H$22,"発注者協議中")</f>
         <v/>
       </c>
       <c r="F6" s="28">
-        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$21,A6,着手前検討事項チェックリスト!$H$5:$H$21,"完了")</f>
+        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$22,A6,着手前検討事項チェックリスト!$H$5:$H$22,"完了")</f>
         <v/>
       </c>
     </row>
@@ -2153,23 +2326,23 @@
         </is>
       </c>
       <c r="B7" s="28">
-        <f>COUNTIF(着手前検討事項チェックリスト!$B$5:$B$21,A7)</f>
+        <f>COUNTIF(着手前検討事項チェックリスト!$B$5:$B$22,A7)</f>
         <v/>
       </c>
       <c r="C7" s="28">
-        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$21,A7,着手前検討事項チェックリスト!$H$5:$H$21,"未着手")</f>
+        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$22,A7,着手前検討事項チェックリスト!$H$5:$H$22,"未着手")</f>
         <v/>
       </c>
       <c r="D7" s="28">
-        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$21,A7,着手前検討事項チェックリスト!$H$5:$H$21,"確認中")</f>
+        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$22,A7,着手前検討事項チェックリスト!$H$5:$H$22,"確認中")</f>
         <v/>
       </c>
       <c r="E7" s="28">
-        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$21,A7,着手前検討事項チェックリスト!$H$5:$H$21,"発注者協議中")</f>
+        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$22,A7,着手前検討事項チェックリスト!$H$5:$H$22,"発注者協議中")</f>
         <v/>
       </c>
       <c r="F7" s="28">
-        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$21,A7,着手前検討事項チェックリスト!$H$5:$H$21,"完了")</f>
+        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$22,A7,着手前検討事項チェックリスト!$H$5:$H$22,"完了")</f>
         <v/>
       </c>
     </row>
@@ -2180,23 +2353,23 @@
         </is>
       </c>
       <c r="B8" s="28">
-        <f>COUNTIF(着手前検討事項チェックリスト!$B$5:$B$21,A8)</f>
+        <f>COUNTIF(着手前検討事項チェックリスト!$B$5:$B$22,A8)</f>
         <v/>
       </c>
       <c r="C8" s="28">
-        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$21,A8,着手前検討事項チェックリスト!$H$5:$H$21,"未着手")</f>
+        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$22,A8,着手前検討事項チェックリスト!$H$5:$H$22,"未着手")</f>
         <v/>
       </c>
       <c r="D8" s="28">
-        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$21,A8,着手前検討事項チェックリスト!$H$5:$H$21,"確認中")</f>
+        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$22,A8,着手前検討事項チェックリスト!$H$5:$H$22,"確認中")</f>
         <v/>
       </c>
       <c r="E8" s="28">
-        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$21,A8,着手前検討事項チェックリスト!$H$5:$H$21,"発注者協議中")</f>
+        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$22,A8,着手前検討事項チェックリスト!$H$5:$H$22,"発注者協議中")</f>
         <v/>
       </c>
       <c r="F8" s="28">
-        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$21,A8,着手前検討事項チェックリスト!$H$5:$H$21,"完了")</f>
+        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$22,A8,着手前検討事項チェックリスト!$H$5:$H$22,"完了")</f>
         <v/>
       </c>
     </row>
@@ -2207,23 +2380,23 @@
         </is>
       </c>
       <c r="B9" s="28">
-        <f>COUNTIF(着手前検討事項チェックリスト!$B$5:$B$21,A9)</f>
+        <f>COUNTIF(着手前検討事項チェックリスト!$B$5:$B$22,A9)</f>
         <v/>
       </c>
       <c r="C9" s="28">
-        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$21,A9,着手前検討事項チェックリスト!$H$5:$H$21,"未着手")</f>
+        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$22,A9,着手前検討事項チェックリスト!$H$5:$H$22,"未着手")</f>
         <v/>
       </c>
       <c r="D9" s="28">
-        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$21,A9,着手前検討事項チェックリスト!$H$5:$H$21,"確認中")</f>
+        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$22,A9,着手前検討事項チェックリスト!$H$5:$H$22,"確認中")</f>
         <v/>
       </c>
       <c r="E9" s="28">
-        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$21,A9,着手前検討事項チェックリスト!$H$5:$H$21,"発注者協議中")</f>
+        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$22,A9,着手前検討事項チェックリスト!$H$5:$H$22,"発注者協議中")</f>
         <v/>
       </c>
       <c r="F9" s="28">
-        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$21,A9,着手前検討事項チェックリスト!$H$5:$H$21,"完了")</f>
+        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$22,A9,着手前検討事項チェックリスト!$H$5:$H$22,"完了")</f>
         <v/>
       </c>
     </row>
@@ -2234,23 +2407,23 @@
         </is>
       </c>
       <c r="B10" s="28">
-        <f>COUNTIF(着手前検討事項チェックリスト!$B$5:$B$21,A10)</f>
+        <f>COUNTIF(着手前検討事項チェックリスト!$B$5:$B$22,A10)</f>
         <v/>
       </c>
       <c r="C10" s="28">
-        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$21,A10,着手前検討事項チェックリスト!$H$5:$H$21,"未着手")</f>
+        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$22,A10,着手前検討事項チェックリスト!$H$5:$H$22,"未着手")</f>
         <v/>
       </c>
       <c r="D10" s="28">
-        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$21,A10,着手前検討事項チェックリスト!$H$5:$H$21,"確認中")</f>
+        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$22,A10,着手前検討事項チェックリスト!$H$5:$H$22,"確認中")</f>
         <v/>
       </c>
       <c r="E10" s="28">
-        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$21,A10,着手前検討事項チェックリスト!$H$5:$H$21,"発注者協議中")</f>
+        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$22,A10,着手前検討事項チェックリスト!$H$5:$H$22,"発注者協議中")</f>
         <v/>
       </c>
       <c r="F10" s="28">
-        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$21,A10,着手前検討事項チェックリスト!$H$5:$H$21,"完了")</f>
+        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$22,A10,着手前検討事項チェックリスト!$H$5:$H$22,"完了")</f>
         <v/>
       </c>
     </row>
@@ -2261,23 +2434,23 @@
         </is>
       </c>
       <c r="B11" s="28">
-        <f>COUNTIF(着手前検討事項チェックリスト!$B$5:$B$21,A11)</f>
+        <f>COUNTIF(着手前検討事項チェックリスト!$B$5:$B$22,A11)</f>
         <v/>
       </c>
       <c r="C11" s="28">
-        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$21,A11,着手前検討事項チェックリスト!$H$5:$H$21,"未着手")</f>
+        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$22,A11,着手前検討事項チェックリスト!$H$5:$H$22,"未着手")</f>
         <v/>
       </c>
       <c r="D11" s="28">
-        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$21,A11,着手前検討事項チェックリスト!$H$5:$H$21,"確認中")</f>
+        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$22,A11,着手前検討事項チェックリスト!$H$5:$H$22,"確認中")</f>
         <v/>
       </c>
       <c r="E11" s="28">
-        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$21,A11,着手前検討事項チェックリスト!$H$5:$H$21,"発注者協議中")</f>
+        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$22,A11,着手前検討事項チェックリスト!$H$5:$H$22,"発注者協議中")</f>
         <v/>
       </c>
       <c r="F11" s="28">
-        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$21,A11,着手前検討事項チェックリスト!$H$5:$H$21,"完了")</f>
+        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$22,A11,着手前検討事項チェックリスト!$H$5:$H$22,"完了")</f>
         <v/>
       </c>
     </row>
@@ -2288,23 +2461,23 @@
         </is>
       </c>
       <c r="B12" s="28">
-        <f>COUNTIF(着手前検討事項チェックリスト!$B$5:$B$21,A12)</f>
+        <f>COUNTIF(着手前検討事項チェックリスト!$B$5:$B$22,A12)</f>
         <v/>
       </c>
       <c r="C12" s="28">
-        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$21,A12,着手前検討事項チェックリスト!$H$5:$H$21,"未着手")</f>
+        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$22,A12,着手前検討事項チェックリスト!$H$5:$H$22,"未着手")</f>
         <v/>
       </c>
       <c r="D12" s="28">
-        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$21,A12,着手前検討事項チェックリスト!$H$5:$H$21,"確認中")</f>
+        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$22,A12,着手前検討事項チェックリスト!$H$5:$H$22,"確認中")</f>
         <v/>
       </c>
       <c r="E12" s="28">
-        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$21,A12,着手前検討事項チェックリスト!$H$5:$H$21,"発注者協議中")</f>
+        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$22,A12,着手前検討事項チェックリスト!$H$5:$H$22,"発注者協議中")</f>
         <v/>
       </c>
       <c r="F12" s="28">
-        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$21,A12,着手前検討事項チェックリスト!$H$5:$H$21,"完了")</f>
+        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$22,A12,着手前検討事項チェックリスト!$H$5:$H$22,"完了")</f>
         <v/>
       </c>
     </row>
@@ -2315,23 +2488,23 @@
         </is>
       </c>
       <c r="B13" s="28">
-        <f>COUNTIF(着手前検討事項チェックリスト!$B$5:$B$21,A13)</f>
+        <f>COUNTIF(着手前検討事項チェックリスト!$B$5:$B$22,A13)</f>
         <v/>
       </c>
       <c r="C13" s="28">
-        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$21,A13,着手前検討事項チェックリスト!$H$5:$H$21,"未着手")</f>
+        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$22,A13,着手前検討事項チェックリスト!$H$5:$H$22,"未着手")</f>
         <v/>
       </c>
       <c r="D13" s="28">
-        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$21,A13,着手前検討事項チェックリスト!$H$5:$H$21,"確認中")</f>
+        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$22,A13,着手前検討事項チェックリスト!$H$5:$H$22,"確認中")</f>
         <v/>
       </c>
       <c r="E13" s="28">
-        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$21,A13,着手前検討事項チェックリスト!$H$5:$H$21,"発注者協議中")</f>
+        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$22,A13,着手前検討事項チェックリスト!$H$5:$H$22,"発注者協議中")</f>
         <v/>
       </c>
       <c r="F13" s="28">
-        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$21,A13,着手前検討事項チェックリスト!$H$5:$H$21,"完了")</f>
+        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$22,A13,着手前検討事項チェックリスト!$H$5:$H$22,"完了")</f>
         <v/>
       </c>
     </row>
@@ -2342,23 +2515,23 @@
         </is>
       </c>
       <c r="B14" s="28">
-        <f>COUNTIF(着手前検討事項チェックリスト!$B$5:$B$21,A14)</f>
+        <f>COUNTIF(着手前検討事項チェックリスト!$B$5:$B$22,A14)</f>
         <v/>
       </c>
       <c r="C14" s="28">
-        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$21,A14,着手前検討事項チェックリスト!$H$5:$H$21,"未着手")</f>
+        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$22,A14,着手前検討事項チェックリスト!$H$5:$H$22,"未着手")</f>
         <v/>
       </c>
       <c r="D14" s="28">
-        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$21,A14,着手前検討事項チェックリスト!$H$5:$H$21,"確認中")</f>
+        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$22,A14,着手前検討事項チェックリスト!$H$5:$H$22,"確認中")</f>
         <v/>
       </c>
       <c r="E14" s="28">
-        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$21,A14,着手前検討事項チェックリスト!$H$5:$H$21,"発注者協議中")</f>
+        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$22,A14,着手前検討事項チェックリスト!$H$5:$H$22,"発注者協議中")</f>
         <v/>
       </c>
       <c r="F14" s="28">
-        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$21,A14,着手前検討事項チェックリスト!$H$5:$H$21,"完了")</f>
+        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$22,A14,着手前検討事項チェックリスト!$H$5:$H$22,"完了")</f>
         <v/>
       </c>
     </row>
@@ -2369,23 +2542,23 @@
         </is>
       </c>
       <c r="B15" s="28">
-        <f>COUNTIF(着手前検討事項チェックリスト!$B$5:$B$21,A15)</f>
+        <f>COUNTIF(着手前検討事項チェックリスト!$B$5:$B$22,A15)</f>
         <v/>
       </c>
       <c r="C15" s="28">
-        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$21,A15,着手前検討事項チェックリスト!$H$5:$H$21,"未着手")</f>
+        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$22,A15,着手前検討事項チェックリスト!$H$5:$H$22,"未着手")</f>
         <v/>
       </c>
       <c r="D15" s="28">
-        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$21,A15,着手前検討事項チェックリスト!$H$5:$H$21,"確認中")</f>
+        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$22,A15,着手前検討事項チェックリスト!$H$5:$H$22,"確認中")</f>
         <v/>
       </c>
       <c r="E15" s="28">
-        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$21,A15,着手前検討事項チェックリスト!$H$5:$H$21,"発注者協議中")</f>
+        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$22,A15,着手前検討事項チェックリスト!$H$5:$H$22,"発注者協議中")</f>
         <v/>
       </c>
       <c r="F15" s="28">
-        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$21,A15,着手前検討事項チェックリスト!$H$5:$H$21,"完了")</f>
+        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$22,A15,着手前検討事項チェックリスト!$H$5:$H$22,"完了")</f>
         <v/>
       </c>
     </row>
@@ -2396,23 +2569,23 @@
         </is>
       </c>
       <c r="B16" s="28">
-        <f>COUNTIF(着手前検討事項チェックリスト!$B$5:$B$21,A16)</f>
+        <f>COUNTIF(着手前検討事項チェックリスト!$B$5:$B$22,A16)</f>
         <v/>
       </c>
       <c r="C16" s="28">
-        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$21,A16,着手前検討事項チェックリスト!$H$5:$H$21,"未着手")</f>
+        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$22,A16,着手前検討事項チェックリスト!$H$5:$H$22,"未着手")</f>
         <v/>
       </c>
       <c r="D16" s="28">
-        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$21,A16,着手前検討事項チェックリスト!$H$5:$H$21,"確認中")</f>
+        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$22,A16,着手前検討事項チェックリスト!$H$5:$H$22,"確認中")</f>
         <v/>
       </c>
       <c r="E16" s="28">
-        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$21,A16,着手前検討事項チェックリスト!$H$5:$H$21,"発注者協議中")</f>
+        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$22,A16,着手前検討事項チェックリスト!$H$5:$H$22,"発注者協議中")</f>
         <v/>
       </c>
       <c r="F16" s="28">
-        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$21,A16,着手前検討事項チェックリスト!$H$5:$H$21,"完了")</f>
+        <f>COUNTIFS(着手前検討事項チェックリスト!$B$5:$B$22,A16,着手前検討事項チェックリスト!$H$5:$H$22,"完了")</f>
         <v/>
       </c>
     </row>
@@ -2443,6 +2616,7 @@
         <v/>
       </c>
     </row>
+    <row r="18"/>
     <row r="19" ht="16.5" customHeight="1" s="47">
       <c r="A19" s="51" t="inlineStr">
         <is>
@@ -2975,31 +3149,32 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="56.1" customHeight="1" s="47">
+    <row r="9" ht="80" customHeight="1" s="47">
       <c r="A9" s="28" t="n"/>
       <c r="B9" s="28" t="inlineStr">
         <is>
-          <t>全工区</t>
+          <t>全工区
+（本工事1・2）</t>
         </is>
       </c>
       <c r="C9" s="48" t="inlineStr">
         <is>
-          <t>伊根町公共残土処分場での重機降り口・残土搬出位置の現地確認（調整漏れ）</t>
+          <t>現場内の重機降り口（想定3～4箇所）の位置確認</t>
         </is>
       </c>
       <c r="D9" s="48" t="inlineStr">
         <is>
-          <t>処分場への重機の降り口及び残土の搬出位置が未調整。処分場管理者と現地で立会・確認し、進入経路・転回場所とあわせて決定する。</t>
+          <t>本工事1 工区①・工区②、本工事2 浚渫北側・浚渫南側の各想定降り口（シート「想定降り口位置図」）を地元立会で確認し、降り口・通行に伴う地元への影響を調整する。</t>
         </is>
       </c>
       <c r="E9" s="48" t="inlineStr">
         <is>
-          <t>伊根町（処分場管理者）</t>
+          <t>地元関係者</t>
         </is>
       </c>
       <c r="F9" s="48" t="inlineStr">
         <is>
-          <t>特記仕様書3-8／現場指摘による追加項目</t>
+          <t>現場指摘による追加項目／想定降口位置図</t>
         </is>
       </c>
     </row>
@@ -3011,4 +3186,45 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="57" t="inlineStr">
+        <is>
+          <t>現場内の重機　想定降り口位置図（赤丸：想定降り口）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="58" t="inlineStr">
+        <is>
+          <t>出典：現場提供の位置図（PDF）より転載。本工事1＝工区①・工区②、本工事2＝浚渫北側工区・浚渫南側工区。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="59" t="inlineStr">
+        <is>
+          <t>■ 本工事1（006宇川）</t>
+        </is>
+      </c>
+      <c r="K3" s="59" t="inlineStr">
+        <is>
+          <t>■ 本工事2（014(097)宇川）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>
--- a/宇川浚渫工事/着手前検討事項拾い出し資料.xlsx
+++ b/宇川浚渫工事/着手前検討事項拾い出し資料.xlsx
@@ -559,6 +559,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -584,6 +587,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -609,6 +615,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -634,6 +643,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2108,7 +2120,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="110" customHeight="1" s="47">
+    <row r="22" ht="125" customHeight="1" s="47">
       <c r="A22" s="19" t="n">
         <v>18</v>
       </c>
@@ -2124,25 +2136,25 @@
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>【調整漏れ】現場内の重機の降り口（河川内への進入位置）の選定</t>
+          <t>【調整漏れ】現場内の重機の降り口（＝残土搬出位置）の設計者（監督職員）への確認</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>想定降り口は3～4箇所で可能（位置図：シート「想定降り口位置図」）。
+          <t>想定降り口は4箇所（位置図：シート「想定降り口位置図」）。降り口は残土搬出位置を兼ねる想定。
 ・本工事1：工区①・工区②の各1箇所（府道654号 井辺平線沿い）
 ・本工事2：浚渫北側工区・浚渫南側工区の各1箇所
-地元立会時に位置を確認し、降り口の仮設（坂路・敷鉄板等）の要否、交通誘導、残土積込み位置とあわせて施工計画に反映する。</t>
+設計した発注者の監督職員に位置の妥当性を確認する必要があり、確認結果により位置・数量・仮設（坂路・敷鉄板等）が変更となる可能性がある（変更時は設計変更協議）。確定後、地元立会で確認し施工計画に反映する。</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
         <is>
-          <t>監督職員／地元関係者（地元立会）</t>
+          <t>監督職員（設計者）／地元関係者（地元立会）</t>
         </is>
       </c>
       <c r="G22" s="19" t="inlineStr">
         <is>
-          <t>地元立会時</t>
+          <t>着手前（地元立会前）</t>
         </is>
       </c>
       <c r="H22" s="19" t="inlineStr">
@@ -2205,7 +2217,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="21.95" customHeight="1" s="47">
       <c r="A3" s="4" t="inlineStr">
         <is>
@@ -2616,7 +2627,6 @@
         <v/>
       </c>
     </row>
-    <row r="18"/>
     <row r="19" ht="16.5" customHeight="1" s="47">
       <c r="A19" s="51" t="inlineStr">
         <is>
@@ -3159,12 +3169,12 @@
       </c>
       <c r="C9" s="48" t="inlineStr">
         <is>
-          <t>現場内の重機降り口（想定3～4箇所）の位置確認</t>
+          <t>現場内の重機降り口（＝残土搬出位置、想定4箇所）の位置確認</t>
         </is>
       </c>
       <c r="D9" s="48" t="inlineStr">
         <is>
-          <t>本工事1 工区①・工区②、本工事2 浚渫北側・浚渫南側の各想定降り口（シート「想定降り口位置図」）を地元立会で確認し、降り口・通行に伴う地元への影響を調整する。</t>
+          <t>本工事1 工区①・工区②、本工事2 浚渫北側・浚渫南側の各想定降り口（シート「想定降り口位置図」）を地元立会で確認する。位置は監督職員（設計者）の確認後に確定するため、変更となる場合がある。</t>
         </is>
       </c>
       <c r="E9" s="48" t="inlineStr">
@@ -3207,7 +3217,7 @@
     <row r="2">
       <c r="A2" s="58" t="inlineStr">
         <is>
-          <t>出典：現場提供の位置図（PDF）より転載。本工事1＝工区①・工区②、本工事2＝浚渫北側工区・浚渫南側工区。</t>
+          <t>出典：現場提供の位置図（PDF）より転載。想定降り口4箇所（降り口＝残土搬出位置）。位置は監督職員（設計者）への確認により変更となる可能性あり。</t>
         </is>
       </c>
     </row>
